--- a/mountains_enriched (2).xlsx
+++ b/mountains_enriched (2).xlsx
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8091</v>
+        <v>7756</v>
       </c>
     </row>
   </sheetData>

--- a/mountains_enriched (2).xlsx
+++ b/mountains_enriched (2).xlsx
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7756</v>
+        <v>8091</v>
       </c>
     </row>
   </sheetData>
